--- a/docs/data/jp/xlsx/1964.xlsx
+++ b/docs/data/jp/xlsx/1964.xlsx
@@ -14128,7 +14128,7 @@
     <row r="210">
       <c r="A210" s="18" t="inlineStr">
         <is>
-          <t>Decrease Increase In Costs On Uncompleted Construction Contracts And Other Ope CFCNS</t>
+          <t>미성공사 지출금 등 증감액</t>
         </is>
       </c>
       <c r="D210" s="20" t="n">
@@ -18431,7 +18431,7 @@
     <row r="75">
       <c r="A75" s="18" t="inlineStr">
         <is>
-          <t>Costs On Uncompleted Construction Contracts And Other CNS</t>
+          <t>미성공사 지출금 등</t>
         </is>
       </c>
       <c r="E75" s="20" t="n">
